--- a/public/artifacts/jahez-valuation-model.xlsx
+++ b/public/artifacts/jahez-valuation-model.xlsx
@@ -12,7 +12,7 @@
     <sheet sheetId="6" name="Sensitivity" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Comps" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="Scenarios &amp; Risk" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Shariah Screen" state="visible" r:id="rId12"/>
+    <sheet sheetId="9" name="Compliance Screen" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -28,7 +28,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.2
-Open in Faheem — faheem://doc/market-data-comps/2</t>
+Open in Faheem, faheem://doc/market-data-comps/2</t>
         </r>
       </text>
     </comment>
@@ -36,7 +36,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.2
-Open in Faheem — faheem://doc/market-data-comps/2</t>
+Open in Faheem, faheem://doc/market-data-comps/2</t>
         </r>
       </text>
     </comment>
@@ -44,7 +44,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.3
-Open in Faheem — faheem://doc/market-data-comps/3</t>
+Open in Faheem, faheem://doc/market-data-comps/3</t>
         </r>
       </text>
     </comment>
@@ -52,7 +52,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.3
-Open in Faheem — faheem://doc/market-data-comps/3</t>
+Open in Faheem, faheem://doc/market-data-comps/3</t>
         </r>
       </text>
     </comment>
@@ -60,29 +60,29 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.3
-Open in Faheem — faheem://doc/market-data-comps/3
-n/a — insufficient trading history (IPO'd Dec 2024)</t>
+Open in Faheem, faheem://doc/market-data-comps/3
+n/a, insufficient trading history (IPO'd Dec 2024)</t>
         </r>
       </text>
     </comment>
     <comment ref="C10" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: levered beta = comp-set median of DoorDash 1.78 and Delivery Hero 1.86 (Talabat n/a — insufficient trading history), per Market Data &amp; Comparables Snapshot p.3. Jahez's own 0.02 5Y beta is a thin-trading artifact and is NOT used. A bottom-up unlever/relever to Jahez's capital structure is the flagged next step.</t>
+          <t>Assumption, analyst judgment: levered beta = comp-set median of DoorDash 1.78 and Delivery Hero 1.86 (Talabat n/a, insufficient trading history), per Market Data &amp; Comparables Snapshot p.3. Jahez's own 0.02 5Y beta is a thin-trading artifact and is NOT used. A bottom-up unlever/relever to Jahez's capital structure is the flagged next step.</t>
         </r>
       </text>
     </comment>
     <comment ref="C12" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: cost-of-debt spread of +200bps over the risk-free rate. No clean Jahez credit spread is sourceable (Cbonds Saudi IG index is paywalled; the sovereign USD spread of ~50–100bps is sovereign, not corporate). 200bps reflects an unrated but cash-generative KSA mid-cap.</t>
+          <t>Assumption, analyst judgment: cost-of-debt spread of +200bps over the risk-free rate. No clean Jahez credit spread is sourceable (Cbonds Saudi IG index is paywalled; the sovereign USD spread of ~50–100bps is sovereign, not corporate). 200bps reflects an unrated but cash-generative KSA mid-cap.</t>
         </r>
       </text>
     </comment>
     <comment ref="C14" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: Saudi zakat convention ~2.5% of the zakat base for Saudi/GCC-owned entities (vs the 20% CIT that applies to foreign ownership). Q1-26 zakat of SAR 0.12m sat on a pre-zakat loss, so no meaningful effective rate is observable. Applied as the NOPAT tax rate and the debt tax-shield.</t>
+          <t>Assumption, analyst judgment: Saudi zakat convention ~2.5% of the zakat base for Saudi/GCC-owned entities (vs the 20% CIT that applies to foreign ownership). Q1-26 zakat of SAR 0.12m sat on a pre-zakat loss, so no meaningful effective rate is observable. Applied as the NOPAT tax rate and the debt tax-shield.</t>
         </r>
       </text>
     </comment>
@@ -90,7 +90,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q1 2026 Financial Statements, p.24
-Open in Faheem — faheem://doc/q1-26-fs/24
+Open in Faheem, faheem://doc/q1-26-fs/24
 209,836,060 shares at SR 0.5 par (note 9)</t>
         </r>
       </text>
@@ -99,7 +99,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.2
-Open in Faheem — faheem://doc/market-data-comps/2</t>
+Open in Faheem, faheem://doc/market-data-comps/2</t>
         </r>
       </text>
     </comment>
@@ -107,7 +107,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q1 2026 Financial Statements, p.4
-Open in Faheem — faheem://doc/q1-26-fs/4</t>
+Open in Faheem, faheem://doc/q1-26-fs/4</t>
         </r>
       </text>
     </comment>
@@ -115,7 +115,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q1 2026 Financial Statements, p.4
-Open in Faheem — faheem://doc/q1-26-fs/4</t>
+Open in Faheem, faheem://doc/q1-26-fs/4</t>
         </r>
       </text>
     </comment>
@@ -123,49 +123,49 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q1 2026 Financial Statements, p.4
-Open in Faheem — faheem://doc/q1-26-fs/4</t>
+Open in Faheem, faheem://doc/q1-26-fs/4</t>
         </r>
       </text>
     </comment>
     <comment ref="C29" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: long-run nominal terminal growth ~3.0% — broadly Saudi long-term inflation / nominal GDP, below the explicit-period growth and above zero real. Bull 3.5% / Bear 2.5%.</t>
+          <t>Assumption, analyst judgment: long-run nominal terminal growth ~3.0%, broadly Saudi long-term inflation / nominal GDP, below the explicit-period growth and above zero real. Bull 3.5% / Bear 2.5%.</t>
         </r>
       </text>
     </comment>
     <comment ref="C30" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: IRR hold period = 4 years, the mid-point of Lunar's 3–5 year mandate window (see Lunar IC Charter).</t>
+          <t>Assumption, analyst judgment: IRR hold period = 4 years, the mid-point of Lunar's 3–5 year mandate window (see Lunar IC Charter).</t>
         </r>
       </text>
     </comment>
     <comment ref="C31" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: explicit forecast horizon of five years (FY26E–FY30E), then Gordon-growth terminal value.</t>
+          <t>Assumption, analyst judgment: explicit forecast horizon of five years (FY26E–FY30E), then Gordon-growth terminal value.</t>
         </r>
       </text>
     </comment>
     <comment ref="C33" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: D&amp;A held at 3.5% of net revenue (FY25 actual ~3.85%; normalises slightly lower as the IFRS-16 right-of-use base matures).</t>
+          <t>Assumption, analyst judgment: D&amp;A held at 3.5% of net revenue (FY25 actual ~3.85%; normalises slightly lower as the IFRS-16 right-of-use base matures).</t>
         </r>
       </text>
     </comment>
     <comment ref="C34" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: capex at 2.5% of net revenue. No capex line is disclosed in the pack; Jahez is an asset-light platform, so this is set modestly above steady-state maintenance capex.</t>
+          <t>Assumption, analyst judgment: capex at 2.5% of net revenue. No capex line is disclosed in the pack; Jahez is an asset-light platform, so this is set modestly above steady-state maintenance capex.</t>
         </r>
       </text>
     </comment>
     <comment ref="C35" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: ΔNWC drag at 2.0% of the change in net revenue. Delivery platforms run negative-to-near-zero working capital (collect from diners fast, settle restaurants/riders later); a small 2% drag on incremental revenue is deliberately conservative.</t>
+          <t>Assumption, analyst judgment: ΔNWC drag at 2.0% of the change in net revenue. Delivery platforms run negative-to-near-zero working capital (collect from diners fast, settle restaurants/riders later); a small 2% drag on incremental revenue is deliberately conservative.</t>
         </r>
       </text>
     </comment>
@@ -183,7 +183,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Annual Report 2024, p.24
-Open in Faheem — faheem://doc/fy24-ar/24</t>
+Open in Faheem, faheem://doc/fy24-ar/24</t>
         </r>
       </text>
     </comment>
@@ -191,7 +191,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.4
-Open in Faheem — faheem://doc/fy25-er/4</t>
+Open in Faheem, faheem://doc/fy25-er/4</t>
         </r>
       </text>
     </comment>
@@ -199,42 +199,42 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.4
-Open in Faheem — faheem://doc/fy25-er/4</t>
+Open in Faheem, faheem://doc/fy25-er/4</t>
         </r>
       </text>
     </comment>
     <comment ref="F5" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: order growth FY26E +18% (Snoonu full-year consolidation from Oct-2025 plus organic; Q1-26 orders +21% YoY), tapering toward +6% single-market maturity by FY30E.</t>
+          <t>Assumption, analyst judgment: order growth FY26E +18% (Snoonu full-year consolidation from Oct-2025 plus organic; Q1-26 orders +21% YoY), tapering toward +6% single-market maturity by FY30E.</t>
         </r>
       </text>
     </comment>
     <comment ref="G5" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: order growth FY26E +18% (Snoonu full-year consolidation from Oct-2025 plus organic; Q1-26 orders +21% YoY), tapering toward +6% single-market maturity by FY30E.</t>
+          <t>Assumption, analyst judgment: order growth FY26E +18% (Snoonu full-year consolidation from Oct-2025 plus organic; Q1-26 orders +21% YoY), tapering toward +6% single-market maturity by FY30E.</t>
         </r>
       </text>
     </comment>
     <comment ref="H5" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: order growth FY26E +18% (Snoonu full-year consolidation from Oct-2025 plus organic; Q1-26 orders +21% YoY), tapering toward +6% single-market maturity by FY30E.</t>
+          <t>Assumption, analyst judgment: order growth FY26E +18% (Snoonu full-year consolidation from Oct-2025 plus organic; Q1-26 orders +21% YoY), tapering toward +6% single-market maturity by FY30E.</t>
         </r>
       </text>
     </comment>
     <comment ref="I5" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: order growth FY26E +18% (Snoonu full-year consolidation from Oct-2025 plus organic; Q1-26 orders +21% YoY), tapering toward +6% single-market maturity by FY30E.</t>
+          <t>Assumption, analyst judgment: order growth FY26E +18% (Snoonu full-year consolidation from Oct-2025 plus organic; Q1-26 orders +21% YoY), tapering toward +6% single-market maturity by FY30E.</t>
         </r>
       </text>
     </comment>
     <comment ref="J5" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: order growth FY26E +18% (Snoonu full-year consolidation from Oct-2025 plus organic; Q1-26 orders +21% YoY), tapering toward +6% single-market maturity by FY30E.</t>
+          <t>Assumption, analyst judgment: order growth FY26E +18% (Snoonu full-year consolidation from Oct-2025 plus organic; Q1-26 orders +21% YoY), tapering toward +6% single-market maturity by FY30E.</t>
         </r>
       </text>
     </comment>
@@ -242,7 +242,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Annual Report 2024, p.24
-Open in Faheem — faheem://doc/fy24-ar/24</t>
+Open in Faheem, faheem://doc/fy24-ar/24</t>
         </r>
       </text>
     </comment>
@@ -250,7 +250,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.4
-Open in Faheem — faheem://doc/fy25-er/4</t>
+Open in Faheem, faheem://doc/fy25-er/4</t>
         </r>
       </text>
     </comment>
@@ -258,42 +258,42 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.4
-Open in Faheem — faheem://doc/fy25-er/4</t>
+Open in Faheem, faheem://doc/fy25-er/4</t>
         </r>
       </text>
     </comment>
     <comment ref="F7" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: AOV growth FY26E +6% (basket-mix + inflation; Q1-26 AOV +15% YoY on Snoonu mix), tapering to +3%.</t>
+          <t>Assumption, analyst judgment: AOV growth FY26E +6% (basket-mix + inflation; Q1-26 AOV +15% YoY on Snoonu mix), tapering to +3%.</t>
         </r>
       </text>
     </comment>
     <comment ref="G7" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: AOV growth FY26E +6% (basket-mix + inflation; Q1-26 AOV +15% YoY on Snoonu mix), tapering to +3%.</t>
+          <t>Assumption, analyst judgment: AOV growth FY26E +6% (basket-mix + inflation; Q1-26 AOV +15% YoY on Snoonu mix), tapering to +3%.</t>
         </r>
       </text>
     </comment>
     <comment ref="H7" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: AOV growth FY26E +6% (basket-mix + inflation; Q1-26 AOV +15% YoY on Snoonu mix), tapering to +3%.</t>
+          <t>Assumption, analyst judgment: AOV growth FY26E +6% (basket-mix + inflation; Q1-26 AOV +15% YoY on Snoonu mix), tapering to +3%.</t>
         </r>
       </text>
     </comment>
     <comment ref="I7" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: AOV growth FY26E +6% (basket-mix + inflation; Q1-26 AOV +15% YoY on Snoonu mix), tapering to +3%.</t>
+          <t>Assumption, analyst judgment: AOV growth FY26E +6% (basket-mix + inflation; Q1-26 AOV +15% YoY on Snoonu mix), tapering to +3%.</t>
         </r>
       </text>
     </comment>
     <comment ref="J7" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: AOV growth FY26E +6% (basket-mix + inflation; Q1-26 AOV +15% YoY on Snoonu mix), tapering to +3%.</t>
+          <t>Assumption, analyst judgment: AOV growth FY26E +6% (basket-mix + inflation; Q1-26 AOV +15% YoY on Snoonu mix), tapering to +3%.</t>
         </r>
       </text>
     </comment>
@@ -301,7 +301,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Annual Report 2024, p.24
-Open in Faheem — faheem://doc/fy24-ar/24
+Open in Faheem, faheem://doc/fy24-ar/24
 Actuals reported; orders×AOV ties within rounding.</t>
         </r>
       </text>
@@ -310,7 +310,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.4
-Open in Faheem — faheem://doc/fy25-er/4
+Open in Faheem, faheem://doc/fy25-er/4
 Actuals reported; orders×AOV ties within rounding.</t>
         </r>
       </text>
@@ -319,7 +319,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.4
-Open in Faheem — faheem://doc/fy25-er/4
+Open in Faheem, faheem://doc/fy25-er/4
 Actuals reported; orders×AOV ties within rounding.</t>
         </r>
       </text>
@@ -362,35 +362,35 @@
     <comment ref="F9" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: net-revenue monetisation (net revenue / GMV) eases from FY25's 32.1% to 31.0% in FY26E then holds at 30.5% — reflecting continued delivery-fee competition (KSA platform revenue fell 8.6% YoY in FY25) before stabilising.</t>
+          <t>Assumption, analyst judgment: net-revenue monetisation (net revenue / GMV) eases from FY25's 32.1% to 31.0% in FY26E then holds at 30.5%, reflecting continued delivery-fee competition (KSA platform revenue fell 8.6% YoY in FY25) before stabilising.</t>
         </r>
       </text>
     </comment>
     <comment ref="G9" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: net-revenue monetisation (net revenue / GMV) eases from FY25's 32.1% to 31.0% in FY26E then holds at 30.5% — reflecting continued delivery-fee competition (KSA platform revenue fell 8.6% YoY in FY25) before stabilising.</t>
+          <t>Assumption, analyst judgment: net-revenue monetisation (net revenue / GMV) eases from FY25's 32.1% to 31.0% in FY26E then holds at 30.5%, reflecting continued delivery-fee competition (KSA platform revenue fell 8.6% YoY in FY25) before stabilising.</t>
         </r>
       </text>
     </comment>
     <comment ref="H9" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: net-revenue monetisation (net revenue / GMV) eases from FY25's 32.1% to 31.0% in FY26E then holds at 30.5% — reflecting continued delivery-fee competition (KSA platform revenue fell 8.6% YoY in FY25) before stabilising.</t>
+          <t>Assumption, analyst judgment: net-revenue monetisation (net revenue / GMV) eases from FY25's 32.1% to 31.0% in FY26E then holds at 30.5%, reflecting continued delivery-fee competition (KSA platform revenue fell 8.6% YoY in FY25) before stabilising.</t>
         </r>
       </text>
     </comment>
     <comment ref="I9" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: net-revenue monetisation (net revenue / GMV) eases from FY25's 32.1% to 31.0% in FY26E then holds at 30.5% — reflecting continued delivery-fee competition (KSA platform revenue fell 8.6% YoY in FY25) before stabilising.</t>
+          <t>Assumption, analyst judgment: net-revenue monetisation (net revenue / GMV) eases from FY25's 32.1% to 31.0% in FY26E then holds at 30.5%, reflecting continued delivery-fee competition (KSA platform revenue fell 8.6% YoY in FY25) before stabilising.</t>
         </r>
       </text>
     </comment>
     <comment ref="J9" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: net-revenue monetisation (net revenue / GMV) eases from FY25's 32.1% to 31.0% in FY26E then holds at 30.5% — reflecting continued delivery-fee competition (KSA platform revenue fell 8.6% YoY in FY25) before stabilising.</t>
+          <t>Assumption, analyst judgment: net-revenue monetisation (net revenue / GMV) eases from FY25's 32.1% to 31.0% in FY26E then holds at 30.5%, reflecting continued delivery-fee competition (KSA platform revenue fell 8.6% YoY in FY25) before stabilising.</t>
         </r>
       </text>
     </comment>
@@ -398,7 +398,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Annual Report 2024, p.5
-Open in Faheem — faheem://doc/fy24-ar/5</t>
+Open in Faheem, faheem://doc/fy24-ar/5</t>
         </r>
       </text>
     </comment>
@@ -406,7 +406,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.4
-Open in Faheem — faheem://doc/fy25-er/4</t>
+Open in Faheem, faheem://doc/fy25-er/4</t>
         </r>
       </text>
     </comment>
@@ -414,7 +414,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.4
-Open in Faheem — faheem://doc/fy25-er/4</t>
+Open in Faheem, faheem://doc/fy25-er/4</t>
         </r>
       </text>
     </comment>
@@ -457,7 +457,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Annual Report 2024, p.24
-Open in Faheem — faheem://doc/fy24-ar/24</t>
+Open in Faheem, faheem://doc/fy24-ar/24</t>
         </r>
       </text>
     </comment>
@@ -465,7 +465,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Annual Report 2024, p.5
-Open in Faheem — faheem://doc/fy24-ar/5</t>
+Open in Faheem, faheem://doc/fy24-ar/5</t>
         </r>
       </text>
     </comment>
@@ -473,7 +473,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.11
-Open in Faheem — faheem://doc/fy25-er/11</t>
+Open in Faheem, faheem://doc/fy25-er/11</t>
         </r>
       </text>
     </comment>
@@ -516,7 +516,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.4
-Open in Faheem — faheem://doc/fy25-er/4</t>
+Open in Faheem, faheem://doc/fy25-er/4</t>
         </r>
       </text>
     </comment>
@@ -524,7 +524,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.9
-Open in Faheem — faheem://doc/fy25-er/9</t>
+Open in Faheem, faheem://doc/fy25-er/9</t>
         </r>
       </text>
     </comment>
@@ -532,7 +532,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.9
-Open in Faheem — faheem://doc/fy25-er/9</t>
+Open in Faheem, faheem://doc/fy25-er/9</t>
         </r>
       </text>
     </comment>
@@ -540,7 +540,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.9
-Open in Faheem — faheem://doc/fy25-er/9</t>
+Open in Faheem, faheem://doc/fy25-er/9</t>
         </r>
       </text>
     </comment>
@@ -548,7 +548,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.9
-Open in Faheem — faheem://doc/fy25-er/9</t>
+Open in Faheem, faheem://doc/fy25-er/9</t>
         </r>
       </text>
     </comment>
@@ -628,35 +628,35 @@
     <comment ref="F6" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: EBITDA margin path anchored to management's FY2026 guidance of SAR 200–220m adj. EBITDA (~7.5% on forecast revenue), recovering to 12.0% by FY30E as Q4-25 one-offs roll off, Snoonu (FY25 adj. EBITDA +SAR 53.7m, profitable) consolidates for a full year, and operating leverage builds — a terminal margin at ~the FY24 peak plus modest leverage.</t>
+          <t>Assumption, analyst judgment: EBITDA margin path anchored to management's FY2026 guidance of SAR 200–220m adj. EBITDA (~7.5% on forecast revenue), recovering to 12.0% by FY30E as Q4-25 one-offs roll off, Snoonu (FY25 adj. EBITDA +SAR 53.7m, profitable) consolidates for a full year, and operating leverage builds, a terminal margin at ~the FY24 peak plus modest leverage.</t>
         </r>
       </text>
     </comment>
     <comment ref="G6" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: EBITDA margin path anchored to management's FY2026 guidance of SAR 200–220m adj. EBITDA (~7.5% on forecast revenue), recovering to 12.0% by FY30E as Q4-25 one-offs roll off, Snoonu (FY25 adj. EBITDA +SAR 53.7m, profitable) consolidates for a full year, and operating leverage builds — a terminal margin at ~the FY24 peak plus modest leverage.</t>
+          <t>Assumption, analyst judgment: EBITDA margin path anchored to management's FY2026 guidance of SAR 200–220m adj. EBITDA (~7.5% on forecast revenue), recovering to 12.0% by FY30E as Q4-25 one-offs roll off, Snoonu (FY25 adj. EBITDA +SAR 53.7m, profitable) consolidates for a full year, and operating leverage builds, a terminal margin at ~the FY24 peak plus modest leverage.</t>
         </r>
       </text>
     </comment>
     <comment ref="H6" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: EBITDA margin path anchored to management's FY2026 guidance of SAR 200–220m adj. EBITDA (~7.5% on forecast revenue), recovering to 12.0% by FY30E as Q4-25 one-offs roll off, Snoonu (FY25 adj. EBITDA +SAR 53.7m, profitable) consolidates for a full year, and operating leverage builds — a terminal margin at ~the FY24 peak plus modest leverage.</t>
+          <t>Assumption, analyst judgment: EBITDA margin path anchored to management's FY2026 guidance of SAR 200–220m adj. EBITDA (~7.5% on forecast revenue), recovering to 12.0% by FY30E as Q4-25 one-offs roll off, Snoonu (FY25 adj. EBITDA +SAR 53.7m, profitable) consolidates for a full year, and operating leverage builds, a terminal margin at ~the FY24 peak plus modest leverage.</t>
         </r>
       </text>
     </comment>
     <comment ref="I6" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: EBITDA margin path anchored to management's FY2026 guidance of SAR 200–220m adj. EBITDA (~7.5% on forecast revenue), recovering to 12.0% by FY30E as Q4-25 one-offs roll off, Snoonu (FY25 adj. EBITDA +SAR 53.7m, profitable) consolidates for a full year, and operating leverage builds — a terminal margin at ~the FY24 peak plus modest leverage.</t>
+          <t>Assumption, analyst judgment: EBITDA margin path anchored to management's FY2026 guidance of SAR 200–220m adj. EBITDA (~7.5% on forecast revenue), recovering to 12.0% by FY30E as Q4-25 one-offs roll off, Snoonu (FY25 adj. EBITDA +SAR 53.7m, profitable) consolidates for a full year, and operating leverage builds, a terminal margin at ~the FY24 peak plus modest leverage.</t>
         </r>
       </text>
     </comment>
     <comment ref="J6" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: EBITDA margin path anchored to management's FY2026 guidance of SAR 200–220m adj. EBITDA (~7.5% on forecast revenue), recovering to 12.0% by FY30E as Q4-25 one-offs roll off, Snoonu (FY25 adj. EBITDA +SAR 53.7m, profitable) consolidates for a full year, and operating leverage builds — a terminal margin at ~the FY24 peak plus modest leverage.</t>
+          <t>Assumption, analyst judgment: EBITDA margin path anchored to management's FY2026 guidance of SAR 200–220m adj. EBITDA (~7.5% on forecast revenue), recovering to 12.0% by FY30E as Q4-25 one-offs roll off, Snoonu (FY25 adj. EBITDA +SAR 53.7m, profitable) consolidates for a full year, and operating leverage builds, a terminal margin at ~the FY24 peak plus modest leverage.</t>
         </r>
       </text>
     </comment>
@@ -664,7 +664,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Annual Report 2024, p.5
-Open in Faheem — faheem://doc/fy24-ar/5</t>
+Open in Faheem, faheem://doc/fy24-ar/5</t>
         </r>
       </text>
     </comment>
@@ -672,7 +672,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.4
-Open in Faheem — faheem://doc/fy25-er/4</t>
+Open in Faheem, faheem://doc/fy25-er/4</t>
         </r>
       </text>
     </comment>
@@ -680,7 +680,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.4
-Open in Faheem — faheem://doc/fy25-er/4</t>
+Open in Faheem, faheem://doc/fy25-er/4</t>
         </r>
       </text>
     </comment>
@@ -688,7 +688,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.8
-Open in Faheem — faheem://doc/fy25-er/8</t>
+Open in Faheem, faheem://doc/fy25-er/8</t>
         </r>
       </text>
     </comment>
@@ -696,7 +696,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.8
-Open in Faheem — faheem://doc/fy25-er/8</t>
+Open in Faheem, faheem://doc/fy25-er/8</t>
         </r>
       </text>
     </comment>
@@ -739,7 +739,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Annual Report 2024, p.5
-Open in Faheem — faheem://doc/fy24-ar/5</t>
+Open in Faheem, faheem://doc/fy24-ar/5</t>
         </r>
       </text>
     </comment>
@@ -747,7 +747,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.4
-Open in Faheem — faheem://doc/fy25-er/4</t>
+Open in Faheem, faheem://doc/fy25-er/4</t>
         </r>
       </text>
     </comment>
@@ -755,56 +755,56 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q4 2025 Earnings Results, p.4
-Open in Faheem — faheem://doc/fy25-er/4</t>
+Open in Faheem, faheem://doc/fy25-er/4</t>
         </r>
       </text>
     </comment>
     <comment ref="F10" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: forecast net income simplified to EBIT×(1−zakat); net finance cost is ~nil given the net-cash balance sheet.</t>
+          <t>Assumption, analyst judgment: forecast net income simplified to EBIT×(1−zakat); net finance cost is ~nil given the net-cash balance sheet.</t>
         </r>
       </text>
     </comment>
     <comment ref="G10" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: forecast net income simplified to EBIT×(1−zakat); net finance cost is ~nil given the net-cash balance sheet.</t>
+          <t>Assumption, analyst judgment: forecast net income simplified to EBIT×(1−zakat); net finance cost is ~nil given the net-cash balance sheet.</t>
         </r>
       </text>
     </comment>
     <comment ref="H10" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: forecast net income simplified to EBIT×(1−zakat); net finance cost is ~nil given the net-cash balance sheet.</t>
+          <t>Assumption, analyst judgment: forecast net income simplified to EBIT×(1−zakat); net finance cost is ~nil given the net-cash balance sheet.</t>
         </r>
       </text>
     </comment>
     <comment ref="I10" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: forecast net income simplified to EBIT×(1−zakat); net finance cost is ~nil given the net-cash balance sheet.</t>
+          <t>Assumption, analyst judgment: forecast net income simplified to EBIT×(1−zakat); net finance cost is ~nil given the net-cash balance sheet.</t>
         </r>
       </text>
     </comment>
     <comment ref="J10" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: forecast net income simplified to EBIT×(1−zakat); net finance cost is ~nil given the net-cash balance sheet.</t>
+          <t>Assumption, analyst judgment: forecast net income simplified to EBIT×(1−zakat); net finance cost is ~nil given the net-cash balance sheet.</t>
         </r>
       </text>
     </comment>
     <comment ref="D15" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: actual-year FCFF applies the same capex (2.5%) and ΔNWC (2.0%) assumptions to reported EBIT — capex is not separately disclosed, so this is an estimate, shown for continuity only (it does not feed the DCF).</t>
+          <t>Assumption, analyst judgment: actual-year FCFF applies the same capex (2.5%) and ΔNWC (2.0%) assumptions to reported EBIT, capex is not separately disclosed, so this is an estimate, shown for continuity only (it does not feed the DCF).</t>
         </r>
       </text>
     </comment>
     <comment ref="E15" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: actual-year FCFF applies the same capex (2.5%) and ΔNWC (2.0%) assumptions to reported EBIT — capex is not separately disclosed, so this is an estimate, shown for continuity only (it does not feed the DCF).</t>
+          <t>Assumption, analyst judgment: actual-year FCFF applies the same capex (2.5%) and ΔNWC (2.0%) assumptions to reported EBIT, capex is not separately disclosed, so this is an estimate, shown for continuity only (it does not feed the DCF).</t>
         </r>
       </text>
     </comment>
@@ -847,7 +847,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q1 2026 Financial Statements, p.7
-Open in Faheem — faheem://doc/q1-26-fs/7</t>
+Open in Faheem, faheem://doc/q1-26-fs/7</t>
         </r>
       </text>
     </comment>
@@ -855,14 +855,14 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q1 2026 Financial Statements, p.4
-Open in Faheem — faheem://doc/q1-26-fs/4</t>
+Open in Faheem, faheem://doc/q1-26-fs/4</t>
         </r>
       </text>
     </comment>
     <comment ref="F20" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: forecast cash rolled forward as prior-year cash + FCFF (no dividends/financing modelled — Jahez pays negligible dividends and is net-cash).</t>
+          <t>Assumption, analyst judgment: forecast cash rolled forward as prior-year cash + FCFF (no dividends/financing modelled, Jahez pays negligible dividends and is net-cash).</t>
         </r>
       </text>
     </comment>
@@ -870,14 +870,14 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q1 2026 Financial Statements, p.4
-Open in Faheem — faheem://doc/q1-26-fs/4</t>
+Open in Faheem, faheem://doc/q1-26-fs/4</t>
         </r>
       </text>
     </comment>
     <comment ref="F21" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: interest-bearing debt and lease liabilities held flat at the FY25 audited level across the forecast (no disclosed amortisation schedule).</t>
+          <t>Assumption, analyst judgment: interest-bearing debt and lease liabilities held flat at the FY25 audited level across the forecast (no disclosed amortisation schedule).</t>
         </r>
       </text>
     </comment>
@@ -885,7 +885,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Q1 2026 Financial Statements, p.4
-Open in Faheem — faheem://doc/q1-26-fs/4</t>
+Open in Faheem, faheem://doc/q1-26-fs/4</t>
         </r>
       </text>
     </comment>
@@ -934,7 +934,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.4
-Open in Faheem — faheem://doc/market-data-comps/4</t>
+Open in Faheem, faheem://doc/market-data-comps/4</t>
         </r>
       </text>
     </comment>
@@ -942,7 +942,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.4
-Open in Faheem — faheem://doc/market-data-comps/4</t>
+Open in Faheem, faheem://doc/market-data-comps/4</t>
         </r>
       </text>
     </comment>
@@ -950,14 +950,14 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.4
-Open in Faheem — faheem://doc/market-data-comps/4</t>
+Open in Faheem, faheem://doc/market-data-comps/4</t>
         </r>
       </text>
     </comment>
     <comment ref="F6" authorId="0">
       <text>
         <r>
-          <t>n/a — no matched-period EV/GMV in sources</t>
+          <t>n/a, no matched-period EV/GMV in sources</t>
         </r>
       </text>
     </comment>
@@ -965,7 +965,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.4
-Open in Faheem — faheem://doc/market-data-comps/4</t>
+Open in Faheem, faheem://doc/market-data-comps/4</t>
         </r>
       </text>
     </comment>
@@ -973,7 +973,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.4
-Open in Faheem — faheem://doc/market-data-comps/4</t>
+Open in Faheem, faheem://doc/market-data-comps/4</t>
         </r>
       </text>
     </comment>
@@ -981,14 +981,14 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.4
-Open in Faheem — faheem://doc/market-data-comps/4</t>
+Open in Faheem, faheem://doc/market-data-comps/4</t>
         </r>
       </text>
     </comment>
     <comment ref="F8" authorId="0">
       <text>
         <r>
-          <t>n/a — no matched-period EV/GMV in sources</t>
+          <t>n/a, no matched-period EV/GMV in sources</t>
         </r>
       </text>
     </comment>
@@ -996,7 +996,7 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.4
-Open in Faheem — faheem://doc/market-data-comps/4</t>
+Open in Faheem, faheem://doc/market-data-comps/4</t>
         </r>
       </text>
     </comment>
@@ -1004,21 +1004,21 @@
       <text>
         <r>
           <t xml:space="preserve">Source: Market Data &amp; Comparables Snapshot, p.4
-Open in Faheem — faheem://doc/market-data-comps/4</t>
+Open in Faheem, faheem://doc/market-data-comps/4</t>
         </r>
       </text>
     </comment>
     <comment ref="E9" authorId="0">
       <text>
         <r>
-          <t>n/a — loss-making (TTM), P/E not meaningful</t>
+          <t>n/a, loss-making (TTM), P/E not meaningful</t>
         </r>
       </text>
     </comment>
     <comment ref="F9" authorId="0">
       <text>
         <r>
-          <t>n/a — no matched-period EV/GMV in sources</t>
+          <t>n/a, no matched-period EV/GMV in sources</t>
         </r>
       </text>
     </comment>
@@ -1056,35 +1056,35 @@
     <comment ref="C6" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: scenario probabilities 25% bull / 50% base / 25% bear — analyst's central-case weighting.</t>
+          <t>Assumption, analyst judgment: scenario probabilities 25% bull / 50% base / 25% bear, analyst's central-case weighting.</t>
         </r>
       </text>
     </comment>
     <comment ref="D6" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: scenario probabilities 25% bull / 50% base / 25% bear — analyst's central-case weighting.</t>
+          <t>Assumption, analyst judgment: scenario probabilities 25% bull / 50% base / 25% bear, analyst's central-case weighting.</t>
         </r>
       </text>
     </comment>
     <comment ref="E6" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: scenario probabilities 25% bull / 50% base / 25% bear — analyst's central-case weighting.</t>
+          <t>Assumption, analyst judgment: scenario probabilities 25% bull / 50% base / 25% bear, analyst's central-case weighting.</t>
         </r>
       </text>
     </comment>
     <comment ref="H6" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull terminal growth 3.5%</t>
+          <t>Assumption, analyst judgment: bull terminal growth 3.5%</t>
         </r>
       </text>
     </comment>
     <comment ref="H7" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bear terminal growth 2.5%</t>
+          <t>Assumption, analyst judgment: bear terminal growth 2.5%</t>
         </r>
       </text>
     </comment>
@@ -1098,70 +1098,70 @@
     <comment ref="C13" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="D13" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="E13" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="F13" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="G13" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="C15" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="D15" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="E15" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="F15" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="G15" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
@@ -1175,77 +1175,77 @@
     <comment ref="E23" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: exit convention: the share price converges to intrinsic value at exit, and intrinsic value compounds at the cost of equity over the hold. IRR = (1+Ke)·(value/entry)^(1/years) − 1 — buying at fair value earns Ke; the discount to value is the additional annualised premium.</t>
+          <t>Assumption, analyst judgment: exit convention: the share price converges to intrinsic value at exit, and intrinsic value compounds at the cost of equity over the hold. IRR = (1+Ke)·(value/entry)^(1/years) − 1, buying at fair value earns Ke; the discount to value is the additional annualised premium.</t>
         </r>
       </text>
     </comment>
     <comment ref="C26" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="D26" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="E26" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="F26" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="G26" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="C28" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="D28" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="E28" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="F28" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="G28" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
@@ -1259,77 +1259,77 @@
     <comment ref="E36" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: exit convention: the share price converges to intrinsic value at exit, and intrinsic value compounds at the cost of equity over the hold. IRR = (1+Ke)·(value/entry)^(1/years) − 1 — buying at fair value earns Ke; the discount to value is the additional annualised premium.</t>
+          <t>Assumption, analyst judgment: exit convention: the share price converges to intrinsic value at exit, and intrinsic value compounds at the cost of equity over the hold. IRR = (1+Ke)·(value/entry)^(1/years) − 1, buying at fair value earns Ke; the discount to value is the additional annualised premium.</t>
         </r>
       </text>
     </comment>
     <comment ref="C39" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="D39" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="E39" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="F39" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="G39" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="C41" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="D41" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="E41" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="F41" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
     <comment ref="G41" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
+          <t>Assumption, analyst judgment: bull/bear apply parallel shifts to net-revenue growth (±~3–4pp/yr) and EBITDA margin (±1.5pp) with terminal growth of 3.5% / 2.5%; WACC is held constant to isolate the operating case.</t>
         </r>
       </text>
     </comment>
@@ -1343,91 +1343,91 @@
     <comment ref="E49" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: exit convention: the share price converges to intrinsic value at exit, and intrinsic value compounds at the cost of equity over the hold. IRR = (1+Ke)·(value/entry)^(1/years) − 1 — buying at fair value earns Ke; the discount to value is the additional annualised premium.</t>
+          <t>Assumption, analyst judgment: exit convention: the share price converges to intrinsic value at exit, and intrinsic value compounds at the cost of equity over the hold. IRR = (1+Ke)·(value/entry)^(1/years) − 1, buying at fair value earns Ke; the discount to value is the additional annualised premium.</t>
         </r>
       </text>
     </comment>
     <comment ref="C53" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: probability score 1–5 (analyst)</t>
+          <t>Assumption, analyst judgment: probability score 1–5 (analyst)</t>
         </r>
       </text>
     </comment>
     <comment ref="D53" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: impact score 1–5 (analyst)</t>
+          <t>Assumption, analyst judgment: impact score 1–5 (analyst)</t>
         </r>
       </text>
     </comment>
     <comment ref="C54" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: probability score 1–5 (analyst)</t>
+          <t>Assumption, analyst judgment: probability score 1–5 (analyst)</t>
         </r>
       </text>
     </comment>
     <comment ref="D54" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: impact score 1–5 (analyst)</t>
+          <t>Assumption, analyst judgment: impact score 1–5 (analyst)</t>
         </r>
       </text>
     </comment>
     <comment ref="C55" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: probability score 1–5 (analyst)</t>
+          <t>Assumption, analyst judgment: probability score 1–5 (analyst)</t>
         </r>
       </text>
     </comment>
     <comment ref="D55" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: impact score 1–5 (analyst)</t>
+          <t>Assumption, analyst judgment: impact score 1–5 (analyst)</t>
         </r>
       </text>
     </comment>
     <comment ref="C56" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: probability score 1–5 (analyst)</t>
+          <t>Assumption, analyst judgment: probability score 1–5 (analyst)</t>
         </r>
       </text>
     </comment>
     <comment ref="D56" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: impact score 1–5 (analyst)</t>
+          <t>Assumption, analyst judgment: impact score 1–5 (analyst)</t>
         </r>
       </text>
     </comment>
     <comment ref="C57" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: probability score 1–5 (analyst)</t>
+          <t>Assumption, analyst judgment: probability score 1–5 (analyst)</t>
         </r>
       </text>
     </comment>
     <comment ref="D57" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: impact score 1–5 (analyst)</t>
+          <t>Assumption, analyst judgment: impact score 1–5 (analyst)</t>
         </r>
       </text>
     </comment>
     <comment ref="C58" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: probability score 1–5 (analyst)</t>
+          <t>Assumption, analyst judgment: probability score 1–5 (analyst)</t>
         </r>
       </text>
     </comment>
     <comment ref="D58" authorId="0">
       <text>
         <r>
-          <t>Assumption — analyst judgment: impact score 1–5 (analyst)</t>
+          <t>Assumption, analyst judgment: impact score 1–5 (analyst)</t>
         </r>
       </text>
     </comment>
@@ -1451,7 +1451,7 @@
     <t>Equity Research · Jahez International Company (Tadawul: 6017)</t>
   </si>
   <si>
-    <t>Rating (advisory only — the committee decides)</t>
+    <t>Rating (advisory only, the committee decides)</t>
   </si>
   <si>
     <t>Target price (DCF fair value)</t>
@@ -1472,7 +1472,7 @@
     <t>Hurdle rate (Lunar mandate)</t>
   </si>
   <si>
-    <t>Shariah screen</t>
+    <t>Compliance screen</t>
   </si>
   <si>
     <t>Composite risk (0–10)</t>
@@ -1481,10 +1481,10 @@
     <t>Weighted value / share</t>
   </si>
   <si>
-    <t>All figures are live formulas referencing the model tabs — target price = DCF!Value per share, upside = DCF, IRR &amp; weighted return = Scenarios &amp; Risk, Shariah = Shariah Screen. Advisory only: the Investment Committee decides. Prepared by Faheem for Lunar Investments, 12 Jul 2026. Not investment advice.</t>
-  </si>
-  <si>
-    <t>Lunar Investments · Jahez Group — Valuation Assumptions</t>
+    <t>All figures are live formulas referencing the model tabs, target price = DCF!Value per share, upside = DCF, IRR &amp; weighted return = Scenarios &amp; Risk, Compliance = Compliance Screen. Advisory only: the Investment Committee decides. Prepared by Faheem for Lunar Investments, 12 Jul 2026. Not investment advice.</t>
+  </si>
+  <si>
+    <t>Lunar Investments · Jahez Group, Valuation Assumptions</t>
   </si>
   <si>
     <t>Discount-rate build, terminal assumptions &amp; operating drivers</t>
@@ -1493,7 +1493,7 @@
     <t>1 · WACC build (discount rate)</t>
   </si>
   <si>
-    <t>Risk-free rate — Saudi 'Sah' sukuk proxy</t>
+    <t>Risk-free rate, Saudi 'Sah' sukuk proxy</t>
   </si>
   <si>
     <t>rate</t>
@@ -1502,10 +1502,10 @@
     <t>market-data-comps p.2</t>
   </si>
   <si>
-    <t>Equity risk premium — KSA total ERP (Damodaran)</t>
-  </si>
-  <si>
-    <t>Comp levered beta — DoorDash (DASH), 5Y</t>
+    <t>Equity risk premium, KSA total ERP (Damodaran)</t>
+  </si>
+  <si>
+    <t>Comp levered beta, DoorDash (DASH), 5Y</t>
   </si>
   <si>
     <t>x</t>
@@ -1514,10 +1514,10 @@
     <t>market-data-comps p.3</t>
   </si>
   <si>
-    <t>Comp levered beta — Delivery Hero (DHER), 5Y</t>
-  </si>
-  <si>
-    <t>Comp levered beta — Talabat (TALABAT)</t>
+    <t>Comp levered beta, Delivery Hero (DHER), 5Y</t>
+  </si>
+  <si>
+    <t>Comp levered beta, Talabat (TALABAT)</t>
   </si>
   <si>
     <t>n/a</t>
@@ -1526,13 +1526,13 @@
     <t>beta</t>
   </si>
   <si>
-    <t>Beta used — comp-set median</t>
+    <t>Beta used, comp-set median</t>
   </si>
   <si>
     <t>analyst judgment</t>
   </si>
   <si>
-    <t>Cost of equity — CAPM (rf + β × ERP)</t>
+    <t>Cost of equity, CAPM (rf + β × ERP)</t>
   </si>
   <si>
     <t>Cost-of-debt spread over rf</t>
@@ -1571,7 +1571,7 @@
     <t>SAR m</t>
   </si>
   <si>
-    <t>Interest-bearing debt — Islamic facilities (D)</t>
+    <t>Interest-bearing debt, Islamic facilities (D)</t>
   </si>
   <si>
     <t>q1-26-fs p.4</t>
@@ -1622,19 +1622,19 @@
     <t>4 · Operating drivers &amp; margins (analyst)</t>
   </si>
   <si>
-    <t>D&amp;A — % of net revenue</t>
-  </si>
-  <si>
-    <t>Capex — % of net revenue</t>
-  </si>
-  <si>
-    <t>ΔNWC — % of change in net revenue</t>
-  </si>
-  <si>
-    <t>Sourced cells (grey) carry the source document + page and a faheem:// deep-link into Faheem's viewer. Gold cells are labelled analyst assumptions — hover any cell for its full rationale.</t>
-  </si>
-  <si>
-    <t>Jahez Group — Revenue Drivers</t>
+    <t>D&amp;A, % of net revenue</t>
+  </si>
+  <si>
+    <t>Capex, % of net revenue</t>
+  </si>
+  <si>
+    <t>ΔNWC, % of change in net revenue</t>
+  </si>
+  <si>
+    <t>Sourced cells (grey) carry the source document + page and a faheem:// deep-link into Faheem's viewer. Gold cells are labelled analyst assumptions, hover any cell for its full rationale.</t>
+  </si>
+  <si>
+    <t>Jahez Group, Revenue Drivers</t>
   </si>
   <si>
     <t>Orders × AOV = GMV → monetisation → net revenue · FY23A–FY25A actuals, FY26E–FY30E driven</t>
@@ -1694,10 +1694,10 @@
     <t>FY2025 net-revenue segment split (SAR m)</t>
   </si>
   <si>
-    <t xml:space="preserve">  Platforms — KSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Platforms — Non-KSA</t>
+    <t xml:space="preserve">  Platforms, KSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Platforms, Non-KSA</t>
   </si>
   <si>
     <t xml:space="preserve">  Logistics</t>
@@ -1718,10 +1718,10 @@
     <t>Actuals (grey) sourced from Jahez filings; forecast columns (white) are formula-driven off the gold assumption cells. Segment revenues reconcile to the consolidated group total via inter-segment eliminations.</t>
   </si>
   <si>
-    <t>Jahez Group — Summary 3-Statement</t>
-  </si>
-  <si>
-    <t>P&amp;L · balance sheet · cash flow — FY23A–FY25A actual, FY26E–FY30E projected by formula</t>
+    <t>Jahez Group, Summary 3-Statement</t>
+  </si>
+  <si>
+    <t>P&amp;L · balance sheet · cash flow, FY23A–FY25A actual, FY26E–FY30E projected by formula</t>
   </si>
   <si>
     <t>Profit &amp; loss (SAR m)</t>
@@ -1772,7 +1772,7 @@
     <t>The projected FCFF row is the base of the DCF. Actual-year FCFF applies the same capex/ΔNWC assumptions to reported figures (capex is not separately disclosed) and is shown for continuity only.</t>
   </si>
   <si>
-    <t>Jahez Group — Discounted Cash Flow (FCFF)</t>
+    <t>Jahez Group, Discounted Cash Flow (FCFF)</t>
   </si>
   <si>
     <t>Explicit FY26E–FY30E PV + Gordon terminal value → enterprise value → equity bridge → value per share</t>
@@ -1832,28 +1832,28 @@
     <t>Every value is a live formula: PV factors read Assumptions!WACC, the terminal value uses Gordon growth, and the equity bridge subtracts debt &amp; leases and adds cash. Change any assumption and the whole chain recomputes.</t>
   </si>
   <si>
-    <t>Jahez Group — Sensitivity</t>
-  </si>
-  <si>
-    <t>Live formula grids (no data-table feature) — corners recompute from the DCF's own FCFF stream</t>
-  </si>
-  <si>
-    <t>Value per share (SAR) — WACC (→) × terminal growth (↓)</t>
+    <t>Jahez Group, Sensitivity</t>
+  </si>
+  <si>
+    <t>Live formula grids (no data-table feature), corners recompute from the DCF's own FCFF stream</t>
+  </si>
+  <si>
+    <t>Value per share (SAR), WACC (→) × terminal growth (↓)</t>
   </si>
   <si>
     <t>g \ WACC</t>
   </si>
   <si>
-    <t>FY30E Adj. EBITDA (SAR m) — GMV growth (→) × net-revenue rate (↓)</t>
+    <t>FY30E Adj. EBITDA (SAR m), GMV growth (→) × net-revenue rate (↓)</t>
   </si>
   <si>
     <t>take \ GMV g</t>
   </si>
   <si>
-    <t>Grid 1 cells hold the full DCF closed form — Σ FCFFₜ/(1+WACC)ᵗ + Gordon TV + net cash, all divided by shares — reading each column's WACC and each row's g live. The centre cell equals the DCF value per share exactly.</t>
-  </si>
-  <si>
-    <t>Jahez Group — Trading Comparables</t>
+    <t>Grid 1 cells hold the full DCF closed form, Σ FCFFₜ/(1+WACC)ᵗ + Gordon TV + net cash, all divided by shares, reading each column's WACC and each row's g live. The centre cell equals the DCF value per share exactly.</t>
+  </si>
+  <si>
+    <t>Jahez Group, Trading Comparables</t>
   </si>
   <si>
     <t>Sourced multiples → implied value per share · football field vs DCF · unsourced cells never filled</t>
@@ -1883,7 +1883,7 @@
     <t>Deliveroo (delisted)</t>
   </si>
   <si>
-    <t>Delisted — acquired by DoorDash 2 Oct 2025; no longer a standalone public comp</t>
+    <t>Delisted, acquired by DoorDash 2 Oct 2025; no longer a standalone public comp</t>
   </si>
   <si>
     <t>DoorDash (NASDAQ: DASH)</t>
@@ -1892,7 +1892,7 @@
     <t>Delivery Hero (ETR: DHER)</t>
   </si>
   <si>
-    <t>Implied value per share (SAR) — multiple × Jahez metric, bridged to equity</t>
+    <t>Implied value per share (SAR), multiple × Jahez metric, bridged to equity</t>
   </si>
   <si>
     <t>Jahez FY25A metric (SAR m / SAR)</t>
@@ -1907,25 +1907,25 @@
     <t xml:space="preserve">  Delivery Hero</t>
   </si>
   <si>
-    <t>Football field — implied value range vs DCF</t>
-  </si>
-  <si>
-    <t>Comps implied — minimum</t>
-  </si>
-  <si>
-    <t>Comps implied — median</t>
-  </si>
-  <si>
-    <t>Comps implied — maximum</t>
+    <t>Football field, implied value range vs DCF</t>
+  </si>
+  <si>
+    <t>Comps implied, minimum</t>
+  </si>
+  <si>
+    <t>Comps implied, median</t>
+  </si>
+  <si>
+    <t>Comps implied, maximum</t>
   </si>
   <si>
     <t>DCF value per share</t>
   </si>
   <si>
-    <t>The comp set is deliberately wide (single-market Talabat to scale-premium DoorDash) and trailing metrics are depressed by FY25 one-offs — treat comps as a sense-check on the DCF, not a standalone valuation. EV/GMV and Delivery Hero P/E are 'n/a — not sourced' and are never filled in.</t>
-  </si>
-  <si>
-    <t>Jahez Group — Scenarios &amp; Risk</t>
+    <t>The comp set is deliberately wide (single-market Talabat to scale-premium DoorDash) and trailing metrics are depressed by FY25 one-offs, treat comps as a sense-check on the DCF, not a standalone valuation. EV/GMV and Delivery Hero P/E are 'n/a, not sourced' and are never filled in.</t>
+  </si>
+  <si>
+    <t>Jahez Group, Scenarios &amp; Risk</t>
   </si>
   <si>
     <t>Bull / base / bear DCFs · IRR at entry vs 15% hurdle · scenario-weighted return · quantified risk register</t>
@@ -2078,7 +2078,7 @@
     <t>Bull/base/bear are full FCFF DCFs sharing the WACC build; only the operating drivers and terminal growth differ. IRR uses the documented exit convention (value compounds at Ke; price converges to value). Risk cites reference the Industry &amp; News Pack pages.</t>
   </si>
   <si>
-    <t>Jahez Group — Shariah Screen (AAOIFI-style)</t>
+    <t>Jahez Group, Compliance Screen (AAOIFI-style)</t>
   </si>
   <si>
     <t>Financial-ratio screens by formula from the balance sheet · pass/fail flags</t>
@@ -2111,16 +2111,16 @@
     <t>Cash &amp; interest-bearing securities / market cap</t>
   </si>
   <si>
-    <t>Cash only — interest-bearing securities not separately disclosed; screened on cash (&lt;33%)</t>
+    <t>Cash only, interest-bearing securities not separately disclosed; screened on cash (&lt;33%)</t>
   </si>
   <si>
     <t xml:space="preserve">  Memo: (debt + leases) / market cap</t>
   </si>
   <si>
-    <t>IFRS-16 leases included (stricter view) — still passes</t>
-  </si>
-  <si>
-    <t>Non-permissible income / total revenue</t>
+    <t>IFRS-16 leases included (stricter view), still passes</t>
+  </si>
+  <si>
+    <t>Non-eligible income / total revenue</t>
   </si>
   <si>
     <t>n/d</t>
@@ -2129,13 +2129,13 @@
     <t>PASS*</t>
   </si>
   <si>
-    <t>Not separately disclosed — screened via business-activity test (permissible food delivery/logistics; Islamic financing)</t>
-  </si>
-  <si>
-    <t>Overall Shariah screen</t>
-  </si>
-  <si>
-    <t>* Non-permissible income is not separately disclosed in the filings; per AAOIFI practice the position is screened via the business-activity test rather than a fabricated percentage. Leverage and liquidity screens both pass with wide headroom; the business is permissible and financed through Islamic facilities.</t>
+    <t>Not separately disclosed, screened via business-activity test (eligible food delivery/logistics; Islamic financing)</t>
+  </si>
+  <si>
+    <t>Overall Compliance screen</t>
+  </si>
+  <si>
+    <t>* Non-eligible income is not separately disclosed in the filings; per AAOIFI practice the position is screened via the business-activity test rather than a fabricated percentage. Leverage and liquidity screens both pass with wide headroom; the business is eligible and financed through Islamic facilities.</t>
   </si>
 </sst>
 </file>
@@ -3187,7 +3187,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="12" t="str">
-        <f>'Shariah Screen'!E11</f>
+        <f>'Compliance Screen'!E11</f>
         <v>PASS</v>
       </c>
       <c r="C14" s="13">

--- a/public/artifacts/jahez-valuation-model.xlsx
+++ b/public/artifacts/jahez-valuation-model.xlsx
@@ -1469,7 +1469,7 @@
     <t>Scenario-weighted return</t>
   </si>
   <si>
-    <t>Hurdle rate (Lunar mandate)</t>
+    <t>Benchmark (Lunar mandate)</t>
   </si>
   <si>
     <t>Compliance screen</t>
@@ -1928,7 +1928,7 @@
     <t>Jahez Group, Scenarios &amp; Risk</t>
   </si>
   <si>
-    <t>Bull / base / bear DCFs · IRR at entry vs 15% hurdle · scenario-weighted return · quantified risk register</t>
+    <t>Bull / base / bear DCFs · IRR at entry vs 15% benchmark · scenario-weighted return · quantified risk register</t>
   </si>
   <si>
     <t>Scenario summary</t>

--- a/public/artifacts/jahez-valuation-model.xlsx
+++ b/public/artifacts/jahez-valuation-model.xlsx
@@ -2078,7 +2078,7 @@
     <t>Bull/base/bear are full FCFF DCFs sharing the WACC build; only the operating drivers and terminal growth differ. IRR uses the documented exit convention (value compounds at Ke; price converges to value). Risk cites reference the Industry &amp; News Pack pages.</t>
   </si>
   <si>
-    <t>Jahez Group, Compliance Screen (AAOIFI-style)</t>
+    <t>Jahez Group, Compliance Screen (Lunar IC Charter, SOCPA-endorsed IFRS figures)</t>
   </si>
   <si>
     <t>Financial-ratio screens by formula from the balance sheet · pass/fail flags</t>
@@ -2105,7 +2105,7 @@
     <t>Interest-bearing debt / market cap</t>
   </si>
   <si>
-    <t>Islamic facilities &amp; loans over market value of equity (AAOIFI leverage screen, &lt;33%)</t>
+    <t>Islamic facilities &amp; loans over market value of equity (IC Charter leverage screen, &lt;33%)</t>
   </si>
   <si>
     <t>Cash &amp; interest-bearing securities / market cap</t>
@@ -2135,7 +2135,7 @@
     <t>Overall Compliance screen</t>
   </si>
   <si>
-    <t>* Non-eligible income is not separately disclosed in the filings; per AAOIFI practice the position is screened via the business-activity test rather than a fabricated percentage. Leverage and liquidity screens both pass with wide headroom; the business is eligible and financed through Islamic facilities.</t>
+    <t>* Non-eligible income is not separately disclosed in the filings; per the IC Charter's methodology the position is screened via the business-activity test rather than a fabricated percentage. Leverage and liquidity screens both pass with wide headroom; the business is eligible and financed through Islamic facilities. Reporting basis: IAS 34 / IFRS as endorsed in the Kingdom of Saudi Arabia and SOCPA pronouncements (Q1 2026 FS, p.13, Statement of compliance).</t>
   </si>
 </sst>
 </file>
